--- a/test-attachments/mm-multi-region-servers.xlsx
+++ b/test-attachments/mm-multi-region-servers.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="APAC Region" sheetId="1" r:id="rId1"/>
-    <sheet name="EMEA Region" sheetId="2" r:id="rId2"/>
-    <sheet name="Switches" sheetId="3" r:id="rId3"/>
+    <sheet name="APAC Servers" sheetId="1" r:id="rId1"/>
+    <sheet name="EMEA Servers" sheetId="2" r:id="rId2"/>
+    <sheet name="Core Backbone" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,14 +399,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Server Name</v>
+        <v>Host</v>
       </c>
       <c r="B1" t="str">
-        <v>Zone</v>
+        <v>Region</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
@@ -414,7 +417,10 @@
         <v>apac-srv-1</v>
       </c>
       <c r="B2" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="3">
@@ -422,7 +428,10 @@
         <v>apac-srv-2</v>
       </c>
       <c r="B3" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="4">
@@ -430,7 +439,10 @@
         <v>apac-srv-3</v>
       </c>
       <c r="B4" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="5">
@@ -438,7 +450,10 @@
         <v>apac-srv-4</v>
       </c>
       <c r="B5" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="6">
@@ -446,7 +461,10 @@
         <v>apac-srv-5</v>
       </c>
       <c r="B6" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="7">
@@ -454,7 +472,10 @@
         <v>apac-srv-6</v>
       </c>
       <c r="B7" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +483,10 @@
         <v>apac-srv-7</v>
       </c>
       <c r="B8" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +494,10 @@
         <v>apac-srv-8</v>
       </c>
       <c r="B9" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +505,10 @@
         <v>apac-srv-9</v>
       </c>
       <c r="B10" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +516,10 @@
         <v>apac-srv-10</v>
       </c>
       <c r="B11" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +527,10 @@
         <v>apac-srv-11</v>
       </c>
       <c r="B12" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +538,10 @@
         <v>apac-srv-12</v>
       </c>
       <c r="B13" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +549,10 @@
         <v>apac-srv-13</v>
       </c>
       <c r="B14" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +560,10 @@
         <v>apac-srv-14</v>
       </c>
       <c r="B15" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +571,10 @@
         <v>apac-srv-15</v>
       </c>
       <c r="B16" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="17">
@@ -534,7 +582,10 @@
         <v>apac-srv-16</v>
       </c>
       <c r="B17" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="18">
@@ -542,7 +593,10 @@
         <v>apac-srv-17</v>
       </c>
       <c r="B18" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="19">
@@ -550,7 +604,10 @@
         <v>apac-srv-18</v>
       </c>
       <c r="B19" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="20">
@@ -558,7 +615,10 @@
         <v>apac-srv-19</v>
       </c>
       <c r="B20" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="21">
@@ -566,7 +626,10 @@
         <v>apac-srv-20</v>
       </c>
       <c r="B21" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="22">
@@ -574,7 +637,10 @@
         <v>apac-srv-21</v>
       </c>
       <c r="B22" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="23">
@@ -582,7 +648,10 @@
         <v>apac-srv-22</v>
       </c>
       <c r="B23" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="24">
@@ -590,7 +659,10 @@
         <v>apac-srv-23</v>
       </c>
       <c r="B24" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="25">
@@ -598,7 +670,10 @@
         <v>apac-srv-24</v>
       </c>
       <c r="B25" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="26">
@@ -606,7 +681,10 @@
         <v>apac-srv-25</v>
       </c>
       <c r="B26" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="27">
@@ -614,7 +692,10 @@
         <v>apac-srv-26</v>
       </c>
       <c r="B27" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="28">
@@ -622,7 +703,10 @@
         <v>apac-srv-27</v>
       </c>
       <c r="B28" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="29">
@@ -630,7 +714,10 @@
         <v>apac-srv-28</v>
       </c>
       <c r="B29" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="30">
@@ -638,7 +725,10 @@
         <v>apac-srv-29</v>
       </c>
       <c r="B30" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="31">
@@ -646,7 +736,10 @@
         <v>apac-srv-30</v>
       </c>
       <c r="B31" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="32">
@@ -654,7 +747,10 @@
         <v>apac-srv-31</v>
       </c>
       <c r="B32" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="33">
@@ -662,7 +758,10 @@
         <v>apac-srv-32</v>
       </c>
       <c r="B33" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="34">
@@ -670,7 +769,10 @@
         <v>apac-srv-33</v>
       </c>
       <c r="B34" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="35">
@@ -678,7 +780,10 @@
         <v>apac-srv-34</v>
       </c>
       <c r="B35" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="36">
@@ -686,7 +791,10 @@
         <v>apac-srv-35</v>
       </c>
       <c r="B36" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="37">
@@ -694,7 +802,10 @@
         <v>apac-srv-36</v>
       </c>
       <c r="B37" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="38">
@@ -702,7 +813,10 @@
         <v>apac-srv-37</v>
       </c>
       <c r="B38" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="39">
@@ -710,7 +824,10 @@
         <v>apac-srv-38</v>
       </c>
       <c r="B39" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="40">
@@ -718,7 +835,10 @@
         <v>apac-srv-39</v>
       </c>
       <c r="B40" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="41">
@@ -726,26 +846,32 @@
         <v>apac-srv-40</v>
       </c>
       <c r="B41" t="str">
-        <v>ap-south-1</v>
+        <v>ap-southeast-1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Active Host</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:C41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Server Name</v>
+        <v>Host</v>
       </c>
       <c r="B1" t="str">
-        <v>Zone</v>
+        <v>Region</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
@@ -753,7 +879,10 @@
         <v>emea-srv-1</v>
       </c>
       <c r="B2" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="3">
@@ -761,7 +890,10 @@
         <v>emea-srv-2</v>
       </c>
       <c r="B3" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="4">
@@ -769,7 +901,10 @@
         <v>emea-srv-3</v>
       </c>
       <c r="B4" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="5">
@@ -777,7 +912,10 @@
         <v>emea-srv-4</v>
       </c>
       <c r="B5" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="6">
@@ -785,7 +923,10 @@
         <v>emea-srv-5</v>
       </c>
       <c r="B6" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="7">
@@ -793,7 +934,10 @@
         <v>emea-srv-6</v>
       </c>
       <c r="B7" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="8">
@@ -801,7 +945,10 @@
         <v>emea-srv-7</v>
       </c>
       <c r="B8" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +956,10 @@
         <v>emea-srv-8</v>
       </c>
       <c r="B9" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +967,10 @@
         <v>emea-srv-9</v>
       </c>
       <c r="B10" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="11">
@@ -825,7 +978,10 @@
         <v>emea-srv-10</v>
       </c>
       <c r="B11" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +989,10 @@
         <v>emea-srv-11</v>
       </c>
       <c r="B12" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="13">
@@ -841,7 +1000,10 @@
         <v>emea-srv-12</v>
       </c>
       <c r="B13" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="14">
@@ -849,7 +1011,10 @@
         <v>emea-srv-13</v>
       </c>
       <c r="B14" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="15">
@@ -857,7 +1022,10 @@
         <v>emea-srv-14</v>
       </c>
       <c r="B15" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="16">
@@ -865,7 +1033,10 @@
         <v>emea-srv-15</v>
       </c>
       <c r="B16" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="17">
@@ -873,7 +1044,10 @@
         <v>emea-srv-16</v>
       </c>
       <c r="B17" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="18">
@@ -881,7 +1055,10 @@
         <v>emea-srv-17</v>
       </c>
       <c r="B18" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="19">
@@ -889,7 +1066,10 @@
         <v>emea-srv-18</v>
       </c>
       <c r="B19" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="20">
@@ -897,7 +1077,10 @@
         <v>emea-srv-19</v>
       </c>
       <c r="B20" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="21">
@@ -905,7 +1088,10 @@
         <v>emea-srv-20</v>
       </c>
       <c r="B21" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="22">
@@ -913,7 +1099,10 @@
         <v>emea-srv-21</v>
       </c>
       <c r="B22" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="23">
@@ -921,7 +1110,10 @@
         <v>emea-srv-22</v>
       </c>
       <c r="B23" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="24">
@@ -929,7 +1121,10 @@
         <v>emea-srv-23</v>
       </c>
       <c r="B24" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="25">
@@ -937,7 +1132,10 @@
         <v>emea-srv-24</v>
       </c>
       <c r="B25" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="26">
@@ -945,7 +1143,10 @@
         <v>emea-srv-25</v>
       </c>
       <c r="B26" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="27">
@@ -953,7 +1154,10 @@
         <v>emea-srv-26</v>
       </c>
       <c r="B27" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="28">
@@ -961,7 +1165,10 @@
         <v>emea-srv-27</v>
       </c>
       <c r="B28" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="29">
@@ -969,7 +1176,10 @@
         <v>emea-srv-28</v>
       </c>
       <c r="B29" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="30">
@@ -977,7 +1187,10 @@
         <v>emea-srv-29</v>
       </c>
       <c r="B30" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="31">
@@ -985,7 +1198,10 @@
         <v>emea-srv-30</v>
       </c>
       <c r="B31" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="32">
@@ -993,7 +1209,10 @@
         <v>emea-srv-31</v>
       </c>
       <c r="B32" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="33">
@@ -1001,7 +1220,10 @@
         <v>emea-srv-32</v>
       </c>
       <c r="B33" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="34">
@@ -1009,7 +1231,10 @@
         <v>emea-srv-33</v>
       </c>
       <c r="B34" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="35">
@@ -1017,7 +1242,10 @@
         <v>emea-srv-34</v>
       </c>
       <c r="B35" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Active Host</v>
       </c>
     </row>
     <row r="36">
@@ -1025,79 +1253,185 @@
         <v>emea-srv-35</v>
       </c>
       <c r="B36" t="str">
-        <v>eu-west-1</v>
+        <v>eu-central-1</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Active Host</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>emea-srv-36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>eu-central-1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Active Host</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>emea-srv-37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>eu-central-1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Active Host</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>emea-srv-38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>eu-central-1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Active Host</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>emea-srv-39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>eu-central-1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Active Host</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>emea-srv-40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>eu-central-1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Active Host</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Switch Name</v>
+        <v>Switch Device</v>
       </c>
       <c r="B1" t="str">
-        <v>Zone</v>
+        <v>Location</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sw-global-1</v>
+        <v>bb-sw-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sw-global-2</v>
+        <v>bb-sw-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sw-global-3</v>
+        <v>bb-sw-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sw-global-4</v>
+        <v>bb-sw-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sw-global-5</v>
+        <v>bb-sw-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sw-global-6</v>
+        <v>bb-sw-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Global</v>
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>bb-sw-7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>bb-sw-8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>bb-sw-9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>bb-sw-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>bb-sw-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Global Backbone Switch</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>bb-sw-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Global Backbone Switch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>